--- a/data/seed/portfolio/L-2025-9502/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2025-9502/vypiska_2026-07_09.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J156"/>
+  <dimension ref="A1:J169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -535,197 +535,197 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>46204</v>
+        <v>46206</v>
       </c>
       <c r="B8" t="n">
         <v>100</v>
       </c>
       <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="n">
-        <v>62135000</v>
+        <v>18129000</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Yulduz Qurilish MChJ</t>
+          <t>Farg'ona Qurilish MChJ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>218825442</t>
+          <t>382544262</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20208000266489731001</t>
+          <t>20208000648973157001</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №267/26 от 01.07.2026</t>
+          <t>Предоплата за товар по договору №11/26 от 03.07.2026</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>484235000</v>
+        <v>440229000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>46204</v>
+        <v>46208</v>
       </c>
       <c r="B9" t="n">
         <v>101</v>
       </c>
-      <c r="C9" s="2" t="n"/>
-      <c r="D9" s="2" t="n">
-        <v>16443000</v>
-      </c>
+      <c r="C9" s="2" t="n">
+        <v>68500000</v>
+      </c>
+      <c r="D9" s="2" t="n"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Yulduz Qurilish MChJ</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>218825442</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-9502)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20208000266489731001</t>
+          <t>16307000215835234417</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №296/26 от 01.07.2026</t>
+          <t>Kredit shartnomasi L-2025-9502 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>500678000</v>
+        <v>371729000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B10" t="n">
         <v>102</v>
       </c>
       <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="n">
-        <v>30692000</v>
+        <v>27498000</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Yulduz Qurilish MChJ</t>
+          <t>Farg'ona Qurilish MChJ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>218825442</t>
+          <t>382544262</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000266489731001</t>
+          <t>20208000648973157001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №242/26, QQS 12%</t>
+          <t>Оплата за товар по счет-фактуре №4315 от 06.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>531370000</v>
+        <v>399227000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B11" t="n">
         <v>103</v>
       </c>
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="n">
-        <v>10035000</v>
+        <v>22258000</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Yulduz Qurilish MChJ</t>
+          <t>Farg'ona Qurilish MChJ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>218825442</t>
+          <t>382544262</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20208000266489731001</t>
+          <t>20208000648973157001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №6664 от 02.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за продукцию по дог. №154/26, НДС 12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>541405000</v>
+        <v>421485000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="B12" t="n">
         <v>104</v>
       </c>
-      <c r="C12" s="2" t="n">
-        <v>68500000</v>
-      </c>
-      <c r="D12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n">
+        <v>19554000</v>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-9502)</t>
+          <t>Farg'ona Qurilish MChJ</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>382544262</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>16307000215835234417</t>
+          <t>20208000648973157001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-9502 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>Оплата за продукцию по дог. №120/26, НДС 12%</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>472905000</v>
+        <v>441039000</v>
       </c>
     </row>
     <row r="13">
@@ -737,21 +737,21 @@
       </c>
       <c r="C13" s="2" t="n"/>
       <c r="D13" s="2" t="n">
-        <v>35546000</v>
+        <v>14523000</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Yulduz Qurilish MChJ</t>
+          <t>Andijon Non MChJ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>218825442</t>
+          <t>379389285</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20208000266489731001</t>
+          <t>20208000273400902001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №97/26 от 06.07.2026</t>
+          <t>Оплата за товар по счет-фактуре №7690 от 06.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>508451000</v>
+        <v>455562000</v>
       </c>
     </row>
     <row r="14">
@@ -777,35 +777,35 @@
       </c>
       <c r="C14" s="2" t="n"/>
       <c r="D14" s="2" t="n">
-        <v>14658000</v>
+        <v>11984000</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Yulduz Qurilish MChJ</t>
+          <t>Barakali Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>218825442</t>
+          <t>215122171</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000266489731001</t>
+          <t>20208000909268904001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №180/26, НДС 12%</t>
+          <t>Предоплата за товар по договору №239/26 от 06.07.2026</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>523109000</v>
+        <v>467546000</v>
       </c>
     </row>
     <row r="15">
@@ -817,35 +817,35 @@
       </c>
       <c r="C15" s="2" t="n"/>
       <c r="D15" s="2" t="n">
-        <v>9844000</v>
+        <v>10849000</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bahor Ip-Kalava MChJ</t>
+          <t>Farg'ona Qurilish MChJ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>251151221</t>
+          <t>382544262</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20208000119092689001</t>
+          <t>20208000648973157001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №8369 за поставленный товар</t>
+          <t>Оплата за продукцию по договору №289/26, НДС 12%</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>532953000</v>
+        <v>478395000</v>
       </c>
     </row>
     <row r="16">
@@ -855,37 +855,37 @@
       <c r="B16" t="n">
         <v>108</v>
       </c>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n">
-        <v>6228000</v>
-      </c>
+      <c r="C16" s="2" t="n">
+        <v>29270000</v>
+      </c>
+      <c r="D16" s="2" t="n"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Yangi Hayot Tur Servis MChJ</t>
+          <t>Namangan Non AJ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>325336613</t>
+          <t>349743926</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20208000051657237001</t>
+          <t>20208000314942583001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №59/26, НДС 12%</t>
+          <t>Tovarlar uchun to'lov h/f №124</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>539181000</v>
+        <v>449125000</v>
       </c>
     </row>
     <row r="17">
@@ -916,331 +916,331 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Заработная плата за июнь 2026 г. (перечисление на пластиковые карты)</t>
+          <t>Iyun oyi uchun ish haqi, reestr №7738</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>474439000</v>
+        <v>384383000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B18" t="n">
         <v>110</v>
       </c>
-      <c r="C18" s="2" t="n">
-        <v>121277000</v>
-      </c>
-      <c r="D18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="n">
+        <v>9895000</v>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Yangi Hayot Yog'och MChJ</t>
+          <t>Farg'ona Qurilish MChJ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>374256960</t>
+          <t>382544262</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20208000013645912001</t>
+          <t>20208000648973157001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №179/26</t>
+          <t>Оплата по с/ф №9132 за поставленный товар</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>353162000</v>
+        <v>394278000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B19" t="n">
         <v>111</v>
       </c>
       <c r="C19" s="2" t="n"/>
       <c r="D19" s="2" t="n">
-        <v>7437000</v>
+        <v>42807000</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Yulduz Qurilish MChJ</t>
+          <t>Ishonch Non AJ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>218825442</t>
+          <t>381564267</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20208000266489731001</t>
+          <t>20208000161840949001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №6968 за поставленный товар</t>
+          <t>Mahsulot uchun to'lov, shartn. №48/26, QQS 12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>360599000</v>
+        <v>437085000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B20" t="n">
         <v>112</v>
       </c>
-      <c r="C20" s="2" t="n"/>
-      <c r="D20" s="2" t="n">
-        <v>5605000</v>
-      </c>
+      <c r="C20" s="2" t="n">
+        <v>7922000</v>
+      </c>
+      <c r="D20" s="2" t="n"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Yulduz Qurilish MChJ</t>
+          <t>Qarshi Qurilish MChJ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>218825442</t>
+          <t>342823132</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20208000266489731001</t>
+          <t>20208000283302227001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №1165 за поставленный товар</t>
+          <t>Арендная плата за июль 2026 г. по договору №94/21</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>366204000</v>
+        <v>429163000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B21" t="n">
         <v>113</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>7922000</v>
+        <v>21315000</v>
       </c>
       <c r="D21" s="2" t="n"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ishonch Qurilish Materiallari MChJ</t>
+          <t>Toshkent Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>357452192</t>
+          <t>304206857</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20208000577393673001</t>
+          <t>20208000071377990001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Аренда помещения за июль, дог. №45/22</t>
+          <t>Оплата за упаковочные материалы, с/ф №2050</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>358282000</v>
+        <v>407848000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>46211</v>
+        <v>46213</v>
       </c>
       <c r="B22" t="n">
         <v>114</v>
       </c>
       <c r="C22" s="2" t="n"/>
       <c r="D22" s="2" t="n">
-        <v>4415000</v>
+        <v>85012000</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Guliston Meva Eksport MChJ</t>
+          <t>Farg'ona Qurilish MChJ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>226793892</t>
+          <t>382544262</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20208000572734009001</t>
+          <t>20208000648973157001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №80/26, НДС 12%</t>
+          <t>Yetkazilgantovar uchun to'lov h/f №6095</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>362697000</v>
+        <v>492860000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B23" t="n">
         <v>115</v>
       </c>
-      <c r="C23" s="2" t="n"/>
-      <c r="D23" s="2" t="n">
-        <v>62038000</v>
-      </c>
+      <c r="C23" s="2" t="n">
+        <v>82758000</v>
+      </c>
+      <c r="D23" s="2" t="n"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bahor Ip-Kalava MChJ</t>
+          <t>Namangan Non AJ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>251151221</t>
+          <t>349743926</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000119092689001</t>
+          <t>20208000314942583001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6923</t>
+          <t>Оплата за товары согласно счет-фактуре №7226</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>424735000</v>
+        <v>410102000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>46212</v>
+        <v>46216</v>
       </c>
       <c r="B24" t="n">
         <v>116</v>
       </c>
       <c r="C24" s="2" t="n"/>
       <c r="D24" s="2" t="n">
-        <v>4270000</v>
+        <v>21873000</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Poligraf MChJ</t>
+          <t>Barakali Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>398539178</t>
+          <t>345539163</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20208000678617009001</t>
+          <t>20208000015951773001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>TOVAR UCHUN TO'LOV, H/F №3864 09.07.2026, QQS BILAN</t>
+          <t>Оплата за товар по счет-фактуре №1276 от 13.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>429005000</v>
+        <v>431975000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B25" t="n">
         <v>117</v>
       </c>
       <c r="C25" s="2" t="n"/>
       <c r="D25" s="2" t="n">
-        <v>6581000</v>
+        <v>16655000</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Guliston Meva Eksport MChJ</t>
+          <t>Barakali Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>226793892</t>
+          <t>345539163</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20208000572734009001</t>
+          <t>20208000015951773001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №238/26, НДС 12%</t>
+          <t>Оплата за продукцию по договору №25/26, НДС 12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>435586000</v>
+        <v>448630000</v>
       </c>
     </row>
     <row r="26">
@@ -1252,35 +1252,35 @@
       </c>
       <c r="C26" s="2" t="n"/>
       <c r="D26" s="2" t="n">
-        <v>23429000</v>
+        <v>8482000</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Andijon Qurilish MChJ</t>
+          <t>Andijon Non MChJ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>366670023</t>
+          <t>379389285</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000800474610001</t>
+          <t>20208000273400902001</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №237/26, НДС 12%</t>
+          <t>Предоплата за товар по дог. №198/26 от 13.07.2026</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>459015000</v>
+        <v>457112000</v>
       </c>
     </row>
     <row r="27">
@@ -1290,37 +1290,37 @@
       <c r="B27" t="n">
         <v>119</v>
       </c>
-      <c r="C27" s="2" t="n"/>
-      <c r="D27" s="2" t="n">
-        <v>7311000</v>
-      </c>
+      <c r="C27" s="2" t="n">
+        <v>46999000</v>
+      </c>
+      <c r="D27" s="2" t="n"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Yulduz Qurilish MChJ</t>
+          <t>Farg'ona Avto Savdo XK</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>218825442</t>
+          <t>225696010</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20208000266489731001</t>
+          <t>20208000364591236001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №152/26 от 13.07.2026</t>
+          <t>Оплата за товары согласно с/ф №8093</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>466326000</v>
+        <v>410113000</v>
       </c>
     </row>
     <row r="28">
@@ -1331,36 +1331,36 @@
         <v>120</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>20935000</v>
+        <v>63002000</v>
       </c>
       <c r="D28" s="2" t="n"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Denov Moy MChJ</t>
+          <t>Afrosiyob Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>398308345</t>
+          <t>353917886</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20208000059555391001</t>
+          <t>20208000861700936001</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №23/26 от 13.07.2026, НДС 12%</t>
+          <t>Tovarlar uchun to'lov h/f №2020</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>445391000</v>
+        <v>347111000</v>
       </c>
     </row>
     <row r="29">
@@ -1372,235 +1372,235 @@
       </c>
       <c r="C29" s="2" t="n"/>
       <c r="D29" s="2" t="n">
-        <v>4981000</v>
+        <v>64829000</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Yulduz Qurilish MChJ</t>
+          <t>Barakali Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>218825442</t>
+          <t>215122171</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20208000266489731001</t>
+          <t>20208000909268904001</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №172/26 от 14.07.2026</t>
+          <t>Оплата за продукцию по договору №142/26, НДС 12%</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>450372000</v>
+        <v>411940000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>46218</v>
+        <v>46217</v>
       </c>
       <c r="B30" t="n">
         <v>122</v>
       </c>
       <c r="C30" s="2" t="n"/>
       <c r="D30" s="2" t="n">
-        <v>274006000</v>
+        <v>18544000</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Yulduz Qurilish MChJ</t>
+          <t>Barakali Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>218825442</t>
+          <t>215122171</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20208000266489731001</t>
+          <t>20208000909268904001</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Shartnoma №29/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за товар по договору №256/26 от 14.07.2026</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>724378000</v>
+        <v>430484000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>46218</v>
+        <v>46217</v>
       </c>
       <c r="B31" t="n">
         <v>123</v>
       </c>
-      <c r="C31" s="2" t="n"/>
-      <c r="D31" s="2" t="n">
-        <v>10044000</v>
-      </c>
+      <c r="C31" s="2" t="n">
+        <v>8829000</v>
+      </c>
+      <c r="D31" s="2" t="n"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Andijon Qurilish MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>366670023</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20208000800474610001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №182/26, НДС 12%</t>
+          <t>СОЦИАЛЬНЫЙ НАЛОГ ЗА ИЮНЬ 2026 Г.</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>734422000</v>
+        <v>421655000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>46218</v>
+        <v>46217</v>
       </c>
       <c r="B32" t="n">
         <v>124</v>
       </c>
-      <c r="C32" s="2" t="n"/>
-      <c r="D32" s="2" t="n">
-        <v>8241000</v>
-      </c>
+      <c r="C32" s="2" t="n">
+        <v>8829000</v>
+      </c>
+      <c r="D32" s="2" t="n"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Yulduz Qurilish MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>218825442</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20208000266489731001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №233/26, НДС 12%</t>
+          <t>НАЛОГ НА ДОХОДЫ ФИЗИЧЕСКИХ ЛИЦ ЗА ИЮНЬ 2026 Г.</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>742663000</v>
+        <v>412826000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>46219</v>
+        <v>46218</v>
       </c>
       <c r="B33" t="n">
         <v>125</v>
       </c>
-      <c r="C33" s="2" t="n"/>
-      <c r="D33" s="2" t="n">
-        <v>4263000</v>
-      </c>
+      <c r="C33" s="2" t="n">
+        <v>30716000</v>
+      </c>
+      <c r="D33" s="2" t="n"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Guliston Meva Eksport MChJ</t>
+          <t>Namangan Non AJ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>226793892</t>
+          <t>349743926</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20208000572734009001</t>
+          <t>20208000314942583001</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №82 16.07.2026, QQS bilan</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №254/26</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>746926000</v>
+        <v>382110000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>46219</v>
+        <v>46218</v>
       </c>
       <c r="B34" t="n">
         <v>126</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>8829000</v>
+        <v>54277000</v>
       </c>
       <c r="D34" s="2" t="n"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Farg'ona Avto Savdo XK</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>225696010</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000364591236001</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Уплата социального налога за июнь</t>
+          <t>Предоплата за материалы по договору №119/26</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>738097000</v>
+        <v>327833000</v>
       </c>
     </row>
     <row r="35">
@@ -1610,77 +1610,77 @@
       <c r="B35" t="n">
         <v>127</v>
       </c>
-      <c r="C35" s="2" t="n">
-        <v>8829000</v>
-      </c>
-      <c r="D35" s="2" t="n"/>
+      <c r="C35" s="2" t="n"/>
+      <c r="D35" s="2" t="n">
+        <v>17600000</v>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Barakali Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>215122171</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000909268904001</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Налог на доходы физических лиц за июнь 2026 г.</t>
+          <t>Оплата за продукцию по договору №298/26, НДС 12%</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>729268000</v>
+        <v>345433000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>46223</v>
+        <v>46220</v>
       </c>
       <c r="B36" t="n">
         <v>128</v>
       </c>
       <c r="C36" s="2" t="n"/>
       <c r="D36" s="2" t="n">
-        <v>11205000</v>
+        <v>36864000</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Yulduz Qurilish MChJ</t>
+          <t>Farg'ona Qurilish MChJ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>218825442</t>
+          <t>382544262</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20208000266489731001</t>
+          <t>20208000648973157001</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №9393 от 20.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №5099 от 17.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>740473000</v>
+        <v>382297000</v>
       </c>
     </row>
     <row r="37">
@@ -1690,37 +1690,37 @@
       <c r="B37" t="n">
         <v>129</v>
       </c>
-      <c r="C37" s="2" t="n">
-        <v>26529000</v>
-      </c>
-      <c r="D37" s="2" t="n"/>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2" t="n">
+        <v>37636000</v>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Denov Moy MChJ</t>
+          <t>Ishonch Non AJ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>398308345</t>
+          <t>381564267</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20208000059555391001</t>
+          <t>20208000161840949001</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №88/26</t>
+          <t>Оплата за товар по с/ф №4916 от 20.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>713944000</v>
+        <v>419933000</v>
       </c>
     </row>
     <row r="38">
@@ -1730,37 +1730,37 @@
       <c r="B38" t="n">
         <v>130</v>
       </c>
-      <c r="C38" s="2" t="n">
-        <v>39810000</v>
-      </c>
-      <c r="D38" s="2" t="n"/>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="2" t="n">
+        <v>22530000</v>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Denov Moy MChJ</t>
+          <t>Farg'ona Qurilish MChJ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>398308345</t>
+          <t>382544262</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20208000059555391001</t>
+          <t>20208000648973157001</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №109/26 от 20.07.2026, НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №237/26, QQS 12%</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>674134000</v>
+        <v>442463000</v>
       </c>
     </row>
     <row r="39">
@@ -1770,343 +1770,343 @@
       <c r="B39" t="n">
         <v>131</v>
       </c>
-      <c r="C39" s="2" t="n">
-        <v>58540000</v>
-      </c>
-      <c r="D39" s="2" t="n"/>
+      <c r="C39" s="2" t="n"/>
+      <c r="D39" s="2" t="n">
+        <v>16370000</v>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bunyodkor Tikuv MChJ</t>
+          <t>Farg'ona Qurilish MChJ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>294154199</t>
+          <t>382544262</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20208000787835044001</t>
+          <t>20208000648973157001</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №8535</t>
+          <t>Оплата по счет-фактуре №3904 за поставленный товар</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>615594000</v>
+        <v>458833000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>46224</v>
+        <v>46223</v>
       </c>
       <c r="B40" t="n">
         <v>132</v>
       </c>
       <c r="C40" s="2" t="n"/>
       <c r="D40" s="2" t="n">
-        <v>70622000</v>
+        <v>16192000</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Yangi Hayot Tur Servis MChJ</t>
+          <t>Barakali Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>325336613</t>
+          <t>345539163</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20208000051657237001</t>
+          <t>20208000015951773001</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №239/26 от 21.07.2026</t>
+          <t>Оплата за продукцию по договору №173/26, НДС 12%</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>686216000</v>
+        <v>475025000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>46224</v>
+        <v>46223</v>
       </c>
       <c r="B41" t="n">
         <v>133</v>
       </c>
-      <c r="C41" s="2" t="n">
-        <v>12808000</v>
-      </c>
-      <c r="D41" s="2" t="n"/>
+      <c r="C41" s="2" t="n"/>
+      <c r="D41" s="2" t="n">
+        <v>15172000</v>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Barakali Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>215122171</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000909268904001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>НДС ЗА ИЮНЬ 2026 Г.</t>
+          <t>Оплата по с/ф №9058 за поставленный товар</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>673408000</v>
+        <v>490197000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>46225</v>
+        <v>46223</v>
       </c>
       <c r="B42" t="n">
         <v>134</v>
       </c>
       <c r="C42" s="2" t="n"/>
       <c r="D42" s="2" t="n">
-        <v>44872000</v>
+        <v>14589000</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Yulduz Qurilish MChJ</t>
+          <t>Farg'ona Qurilish MChJ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>218825442</t>
+          <t>382544262</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20208000266489731001</t>
+          <t>20208000648973157001</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №288/26 от 22.07.2026</t>
+          <t>Mahsulot uchun to'lov, shartnoma №249/26, QQS 12%</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>718280000</v>
+        <v>504786000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>46225</v>
+        <v>46223</v>
       </c>
       <c r="B43" t="n">
         <v>135</v>
       </c>
       <c r="C43" s="2" t="n"/>
       <c r="D43" s="2" t="n">
-        <v>33978000</v>
+        <v>8412000</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sarbon Mebel MChJ</t>
+          <t>Farg'ona Qurilish MChJ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>295815642</t>
+          <t>382544262</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20208000741618409001</t>
+          <t>20208000648973157001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №9275 22.07.2026, QQS bilan</t>
+          <t>Оплата по с/ф №6596 за поставленный товар</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>752258000</v>
+        <v>513198000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>46225</v>
+        <v>46223</v>
       </c>
       <c r="B44" t="n">
         <v>136</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>35711000</v>
+        <v>16834000</v>
       </c>
       <c r="D44" s="2" t="n"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Oqtosh Logistik MChJ</t>
+          <t>Namangan Non AJ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>293903073</t>
+          <t>349743926</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20208000103408145001</t>
+          <t>20208000314942583001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №133/26</t>
+          <t>Предоплата за материалы по договору №228/26</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>716547000</v>
+        <v>496364000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>46226</v>
+        <v>46223</v>
       </c>
       <c r="B45" t="n">
         <v>137</v>
       </c>
-      <c r="C45" s="2" t="n"/>
-      <c r="D45" s="2" t="n">
-        <v>29641000</v>
-      </c>
+      <c r="C45" s="2" t="n">
+        <v>28633000</v>
+      </c>
+      <c r="D45" s="2" t="n"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Yulduz Qurilish MChJ</t>
+          <t>Namangan Non AJ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>218825442</t>
+          <t>349743926</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000266489731001</t>
+          <t>20208000314942583001</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №7072 за поставленный товар</t>
+          <t>Предоплата за материалы по договору №38/26</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>746188000</v>
+        <v>467731000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>46226</v>
+        <v>46223</v>
       </c>
       <c r="B46" t="n">
         <v>138</v>
       </c>
-      <c r="C46" s="2" t="n"/>
-      <c r="D46" s="2" t="n">
-        <v>24121000</v>
-      </c>
+      <c r="C46" s="2" t="n">
+        <v>34571000</v>
+      </c>
+      <c r="D46" s="2" t="n"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Yulduz Qurilish MChJ</t>
+          <t>Toshkent Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>218825442</t>
+          <t>304206857</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20208000266489731001</t>
+          <t>20208000071377990001</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №294/26 от 23.07.2026</t>
+          <t>Оплата за транспортные услуги по дог. №256/26</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>770309000</v>
+        <v>433160000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>46226</v>
+        <v>46223</v>
       </c>
       <c r="B47" t="n">
         <v>139</v>
       </c>
-      <c r="C47" s="2" t="n"/>
-      <c r="D47" s="2" t="n">
-        <v>4890000</v>
-      </c>
+      <c r="C47" s="2" t="n">
+        <v>104713000</v>
+      </c>
+      <c r="D47" s="2" t="n"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Yangi Hayot Tur Servis MChJ</t>
+          <t>Toshkent Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>325336613</t>
+          <t>304206857</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20208000051657237001</t>
+          <t>20208000071377990001</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2116,117 +2116,117 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №2572 за поставленный товар</t>
+          <t>Оплата за товары согласно счет-фактуре №9483</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>775199000</v>
+        <v>328447000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>46226</v>
+        <v>46224</v>
       </c>
       <c r="B48" t="n">
         <v>140</v>
       </c>
-      <c r="C48" s="2" t="n">
-        <v>88079000</v>
-      </c>
-      <c r="D48" s="2" t="n"/>
+      <c r="C48" s="2" t="n"/>
+      <c r="D48" s="2" t="n">
+        <v>14124000</v>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Denov Moy MChJ</t>
+          <t>Farg'ona Qurilish MChJ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>398308345</t>
+          <t>382544262</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20208000059555391001</t>
+          <t>20208000648973157001</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №280/26</t>
+          <t>Оплата за продукцию по договору №267/26, НДС 12%</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>687120000</v>
+        <v>342571000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>46227</v>
+        <v>46225</v>
       </c>
       <c r="B49" t="n">
         <v>141</v>
       </c>
-      <c r="C49" s="2" t="n"/>
-      <c r="D49" s="2" t="n">
-        <v>16678000</v>
-      </c>
+      <c r="C49" s="2" t="n">
+        <v>13051000</v>
+      </c>
+      <c r="D49" s="2" t="n"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Guliston Meva Eksport MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>226793892</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000572734009001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №1009</t>
+          <t>Qo'shilgan qiymat solig'i iyun oyi</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>703798000</v>
+        <v>329520000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>46227</v>
+        <v>46225</v>
       </c>
       <c r="B50" t="n">
         <v>142</v>
       </c>
-      <c r="C50" s="2" t="n"/>
-      <c r="D50" s="2" t="n">
-        <v>4687000</v>
-      </c>
+      <c r="C50" s="2" t="n">
+        <v>49189000</v>
+      </c>
+      <c r="D50" s="2" t="n"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Yulduz Qurilish MChJ</t>
+          <t>Afrosiyob Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>218825442</t>
+          <t>353917886</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000266489731001</t>
+          <t>20208000861700936001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2236,91 +2236,91 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №330 за поставленный товар</t>
+          <t>Оплата за сырье по дог. №188/26 от 22.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>708485000</v>
+        <v>280331000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>46230</v>
+        <v>46227</v>
       </c>
       <c r="B51" t="n">
         <v>143</v>
       </c>
       <c r="C51" s="2" t="n"/>
       <c r="D51" s="2" t="n">
-        <v>83992000</v>
+        <v>25939000</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Yulduz Qurilish MChJ</t>
+          <t>Farg'ona Qurilish MChJ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>218825442</t>
+          <t>382544262</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20208000266489731001</t>
+          <t>20208000648973157001</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №98/26, НДС 12%</t>
+          <t>Предоплата за товар по договору №236/26 от 24.07.2026</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>792477000</v>
+        <v>306270000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>46230</v>
+        <v>46227</v>
       </c>
       <c r="B52" t="n">
         <v>144</v>
       </c>
-      <c r="C52" s="2" t="n"/>
-      <c r="D52" s="2" t="n">
-        <v>42275000</v>
-      </c>
+      <c r="C52" s="2" t="n">
+        <v>4951000</v>
+      </c>
+      <c r="D52" s="2" t="n"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Guliston Meva Eksport MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>226793892</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>20208000572734009001</t>
+          <t>20208000252939030001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №197/26 от 27.07.2026</t>
+          <t>Оплата за электроэнергию согласно сету</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>834752000</v>
+        <v>301319000</v>
       </c>
     </row>
     <row r="53">
@@ -2332,35 +2332,35 @@
       </c>
       <c r="C53" s="2" t="n"/>
       <c r="D53" s="2" t="n">
-        <v>17107000</v>
+        <v>8469000</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Yulduz Qurilish MChJ</t>
+          <t>Farg'ona Qurilish MChJ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>218825442</t>
+          <t>382544262</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20208000266489731001</t>
+          <t>20208000648973157001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №7136 за поставленный товар</t>
+          <t>Предоплата за товар по договору №33/26 от 27.07.2026</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>851859000</v>
+        <v>309788000</v>
       </c>
     </row>
     <row r="54">
@@ -2370,23 +2370,23 @@
       <c r="B54" t="n">
         <v>146</v>
       </c>
-      <c r="C54" s="2" t="n"/>
-      <c r="D54" s="2" t="n">
-        <v>13844000</v>
-      </c>
+      <c r="C54" s="2" t="n">
+        <v>17118000</v>
+      </c>
+      <c r="D54" s="2" t="n"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Yulduz Qurilish MChJ</t>
+          <t>Afrosiyob Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>218825442</t>
+          <t>353917886</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20208000266489731001</t>
+          <t>20208000861700936001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2396,331 +2396,331 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №4225 от 27.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за сырье по договору №216/26 от 27.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>865703000</v>
+        <v>292670000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B55" t="n">
         <v>147</v>
       </c>
       <c r="C55" s="2" t="n"/>
       <c r="D55" s="2" t="n">
-        <v>13517000</v>
+        <v>69516000</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Guliston Meva Eksport MChJ</t>
+          <t>Farg'ona Qurilish MChJ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>226793892</t>
+          <t>382544262</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000572734009001</t>
+          <t>20208000648973157001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №475 от 27.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №3730 от 28.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>879220000</v>
+        <v>362186000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B56" t="n">
         <v>148</v>
       </c>
       <c r="C56" s="2" t="n"/>
       <c r="D56" s="2" t="n">
-        <v>5251000</v>
+        <v>17999000</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Yulduz Qurilish MChJ</t>
+          <t>Barakali Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>218825442</t>
+          <t>215122171</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000266489731001</t>
+          <t>20208000909268904001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №1412 за поставленный товар</t>
+          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №2871 ОТ 28.07.2026, В Т.Ч. НДС 12%</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>884471000</v>
+        <v>380185000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B57" t="n">
         <v>149</v>
       </c>
       <c r="C57" s="2" t="n">
-        <v>4951000</v>
+        <v>75805000</v>
       </c>
       <c r="D57" s="2" t="n"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Namangan Non AJ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>349743926</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20208000909446486001</t>
+          <t>20208000314942583001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию за июль 2026 г.</t>
+          <t>Оплата за товары согласно счет-фактуре №3248</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>879520000</v>
+        <v>304380000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B58" t="n">
         <v>150</v>
       </c>
       <c r="C58" s="2" t="n"/>
       <c r="D58" s="2" t="n">
-        <v>32252000</v>
+        <v>193753000</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Yulduz Qurilish MChJ</t>
+          <t>Bog'ishamol Polimer MChJ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>218825442</t>
+          <t>333661320</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000266489731001</t>
+          <t>20208000165723716001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №6669 за поставленный товар</t>
+          <t>ОПЛАТА ЗА ТОВАР ПО С/Ф №6101 ОТ 29.07.2026, В Т.Ч. НДС 12%</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>911772000</v>
+        <v>498133000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B59" t="n">
         <v>151</v>
       </c>
       <c r="C59" s="2" t="n">
-        <v>38633000</v>
+        <v>21390000</v>
       </c>
       <c r="D59" s="2" t="n"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Denov Moy MChJ</t>
+          <t>Afrosiyob Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>398308345</t>
+          <t>353917886</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20208000059555391001</t>
+          <t>20208000861700936001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №2010</t>
+          <t>Оплата за сырье по договору №209/26 от 29.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>873139000</v>
+        <v>476743000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B60" t="n">
         <v>152</v>
       </c>
       <c r="C60" s="2" t="n">
-        <v>490525000</v>
+        <v>250985000</v>
       </c>
       <c r="D60" s="2" t="n"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Denov Moy MChJ</t>
+          <t>Afrosiyob Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>398308345</t>
+          <t>353917886</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20208000059555391001</t>
+          <t>20208000861700936001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №118/26</t>
+          <t>Предоплата за материалы по договору №140/26</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>382614000</v>
+        <v>225758000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>46234</v>
+        <v>46233</v>
       </c>
       <c r="B61" t="n">
         <v>153</v>
       </c>
       <c r="C61" s="2" t="n"/>
       <c r="D61" s="2" t="n">
-        <v>5977000</v>
+        <v>19988000</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Guliston Meva Eksport MChJ</t>
+          <t>Ishonch Non AJ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>226793892</t>
+          <t>381564267</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20208000572734009001</t>
+          <t>20208000161840949001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №66/26 от 31.07.2026</t>
+          <t>Оплата за товар по с/ф №5757 от 30.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>388591000</v>
+        <v>245746000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>46234</v>
+        <v>46233</v>
       </c>
       <c r="B62" t="n">
         <v>154</v>
       </c>
-      <c r="C62" s="2" t="n"/>
-      <c r="D62" s="2" t="n">
-        <v>4235000</v>
-      </c>
+      <c r="C62" s="2" t="n">
+        <v>14083000</v>
+      </c>
+      <c r="D62" s="2" t="n"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bahor Ip-Kalava MChJ</t>
+          <t>Oltin Vodiy Yog'och XK</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>251151221</t>
+          <t>367002358</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000119092689001</t>
+          <t>20208000047461089001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №255/26, НДС 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №1410</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>392826000</v>
+        <v>231663000</v>
       </c>
     </row>
     <row r="63">
@@ -2730,98 +2730,103 @@
       <c r="B63" t="n">
         <v>155</v>
       </c>
-      <c r="C63" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D63" s="2" t="n"/>
+      <c r="C63" s="2" t="n"/>
+      <c r="D63" s="2" t="n">
+        <v>123419000</v>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Andijon Non MChJ</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>379389285</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000273400902001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Комиссия банка за расчетно-кассовое обслуживание за июль</t>
+          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №5406 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>392526000</v>
+        <v>355082000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>46237</v>
+        <v>46234</v>
       </c>
       <c r="B64" t="n">
         <v>156</v>
       </c>
       <c r="C64" s="2" t="n"/>
       <c r="D64" s="2" t="n">
-        <v>247620000</v>
+        <v>26850000</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Yulduz Qurilish MChJ</t>
+          <t>Farg'ona Qurilish MChJ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>218825442</t>
+          <t>382544262</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>20208000266489731001</t>
+          <t>20208000648973157001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №110/26, НДС 12%</t>
+          <t>Предоплата за товар по договору №20/26 от 31.07.2026</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>640146000</v>
+        <v>381932000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>46237</v>
+        <v>46234</v>
       </c>
       <c r="B65" t="n">
         <v>157</v>
       </c>
       <c r="C65" s="2" t="n"/>
       <c r="D65" s="2" t="n">
-        <v>43038000</v>
+        <v>9310000</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Denov Metall MChJ</t>
+          <t>Farg'ona Qurilish MChJ</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>251039941</t>
+          <t>382544262</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>20208000285274216001</t>
+          <t>20208000648973157001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -2831,51 +2836,46 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №9766 от 03.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №8246 от 31.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>683184000</v>
+        <v>391242000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>46237</v>
+        <v>46234</v>
       </c>
       <c r="B66" t="n">
         <v>158</v>
       </c>
-      <c r="C66" s="2" t="n"/>
-      <c r="D66" s="2" t="n">
-        <v>16020000</v>
-      </c>
+      <c r="C66" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D66" s="2" t="n"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Yulduz Qurilish MChJ</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>218825442</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>20208000266489731001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Shartnoma №24/26 bo'yicha oldindan to'lov</t>
+          <t>Bank xizmati uchun komissiya</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>699204000</v>
+        <v>390942000</v>
       </c>
     </row>
     <row r="67">
@@ -2885,37 +2885,37 @@
       <c r="B67" t="n">
         <v>159</v>
       </c>
-      <c r="C67" s="2" t="n">
-        <v>22969000</v>
-      </c>
-      <c r="D67" s="2" t="n"/>
+      <c r="C67" s="2" t="n"/>
+      <c r="D67" s="2" t="n">
+        <v>36117000</v>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Denov Moy MChJ</t>
+          <t>Farg'ona Qurilish MChJ</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>398308345</t>
+          <t>382544262</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>20208000059555391001</t>
+          <t>20208000648973157001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №191/26</t>
+          <t>SHARTNOMA №168/26 BO'YICHA OLDINDAN TO'LOV</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>676235000</v>
+        <v>427059000</v>
       </c>
     </row>
     <row r="68">
@@ -2925,37 +2925,37 @@
       <c r="B68" t="n">
         <v>160</v>
       </c>
-      <c r="C68" s="2" t="n">
-        <v>27007000</v>
-      </c>
-      <c r="D68" s="2" t="n"/>
+      <c r="C68" s="2" t="n"/>
+      <c r="D68" s="2" t="n">
+        <v>27087000</v>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Denov Moy MChJ</t>
+          <t>Andijon Non MChJ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>398308345</t>
+          <t>379389285</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>20208000059555391001</t>
+          <t>20208000273400902001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по дог. №195/26</t>
+          <t>Оплата за продукцию по дог. №42/26, НДС 12%</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>649228000</v>
+        <v>454146000</v>
       </c>
     </row>
     <row r="69">
@@ -2966,76 +2966,76 @@
         <v>161</v>
       </c>
       <c r="C69" s="2" t="n">
-        <v>38548000</v>
+        <v>66327000</v>
       </c>
       <c r="D69" s="2" t="n"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Oqtosh Logistik MChJ</t>
+          <t>Toshkent Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>293903073</t>
+          <t>304206857</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>20208000103408145001</t>
+          <t>20208000071377990001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №7/26</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №70/26</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>610680000</v>
+        <v>387819000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="B70" t="n">
         <v>162</v>
       </c>
-      <c r="C70" s="2" t="n"/>
-      <c r="D70" s="2" t="n">
-        <v>58615000</v>
-      </c>
+      <c r="C70" s="2" t="n">
+        <v>116850000</v>
+      </c>
+      <c r="D70" s="2" t="n"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Yulduz Qurilish MChJ</t>
+          <t>Farg'ona Avto Savdo XK</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>218825442</t>
+          <t>225696010</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>20208000266489731001</t>
+          <t>20208000364591236001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №9801 от 04.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за транспортные услуги по договору №150/26</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>669295000</v>
+        <v>270969000</v>
       </c>
     </row>
     <row r="71">
@@ -3047,35 +3047,35 @@
       </c>
       <c r="C71" s="2" t="n"/>
       <c r="D71" s="2" t="n">
-        <v>6912000</v>
+        <v>60929000</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Yulduz Qurilish MChJ</t>
+          <t>Durdona Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>218825442</t>
+          <t>203994162</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>20208000266489731001</t>
+          <t>20208000527421691001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №7714 ОТ 04.08.2026, В Т.Ч. НДС 12%</t>
+          <t>Оплата за продукцию по договору №260/26, НДС 12%</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>676207000</v>
+        <v>331898000</v>
       </c>
     </row>
     <row r="72">
@@ -3086,292 +3086,292 @@
         <v>164</v>
       </c>
       <c r="C72" s="2" t="n">
-        <v>48458000</v>
+        <v>69078000</v>
       </c>
       <c r="D72" s="2" t="n"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Denov Moy MChJ</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>398308345</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000059555391001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №13/26 от 04.08.2026, НДС 12%</t>
+          <t>Перечисление заработной платы за июль 2026 г. согласно реестру №6329</t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>627749000</v>
+        <v>262820000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B73" t="n">
         <v>165</v>
       </c>
       <c r="C73" s="2" t="n">
-        <v>53751000</v>
+        <v>68500000</v>
       </c>
       <c r="D73" s="2" t="n"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Denov Moy MChJ</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>398308345</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-9502)</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000059555391001</t>
+          <t>16307000215835234417</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №77/26</t>
+          <t>Kredit shartnomasi L-2025-9502 bo'yicha navbatdagi to'lov (08.2026)</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>573998000</v>
+        <v>194320000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
-        <v>46238</v>
+        <v>46241</v>
       </c>
       <c r="B74" t="n">
         <v>166</v>
       </c>
       <c r="C74" s="2" t="n">
-        <v>69078000</v>
+        <v>17956000</v>
       </c>
       <c r="D74" s="2" t="n"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Namangan Non AJ</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>349743926</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000314942583001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Заработная плата за июль 2026 г. (перечисление на пластиковые карты)</t>
+          <t>Оплата за упаковочные материалы, с/ф №3084</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>504920000</v>
+        <v>176364000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>46239</v>
+        <v>46244</v>
       </c>
       <c r="B75" t="n">
         <v>167</v>
       </c>
       <c r="C75" s="2" t="n"/>
       <c r="D75" s="2" t="n">
-        <v>5686000</v>
+        <v>68531000</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Guliston Meva Eksport MChJ</t>
+          <t>Barakali Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>226793892</t>
+          <t>215122171</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>20208000572734009001</t>
+          <t>20208000909268904001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №158/26, НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №4246</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>510606000</v>
+        <v>244895000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
-        <v>46239</v>
+        <v>46244</v>
       </c>
       <c r="B76" t="n">
         <v>168</v>
       </c>
       <c r="C76" s="2" t="n">
-        <v>68500000</v>
+        <v>8453000</v>
       </c>
       <c r="D76" s="2" t="n"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-9502)</t>
+          <t>Qarshi Qurilish MChJ</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>342823132</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>16307000215835234417</t>
+          <t>20208000283302227001</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-9502 bo'yicha navbatdagi to'lov (08.2026)</t>
+          <t>Арендная плата за август 2026 г. по договору №94/21</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>442106000</v>
+        <v>236442000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B77" t="n">
         <v>169</v>
       </c>
-      <c r="C77" s="2" t="n"/>
-      <c r="D77" s="2" t="n">
-        <v>17858000</v>
-      </c>
+      <c r="C77" s="2" t="n">
+        <v>76492000</v>
+      </c>
+      <c r="D77" s="2" t="n"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Bahor Ip-Kalava MChJ</t>
+          <t>Namangan Non AJ</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>251151221</t>
+          <t>349743926</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>20208000119092689001</t>
+          <t>20208000314942583001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №5956</t>
+          <t>Оплата за товары согласно счет-фактуре №2133</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>459964000</v>
+        <v>159950000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
-        <v>46241</v>
+        <v>46246</v>
       </c>
       <c r="B78" t="n">
         <v>170</v>
       </c>
-      <c r="C78" s="2" t="n">
-        <v>8453000</v>
-      </c>
-      <c r="D78" s="2" t="n"/>
+      <c r="C78" s="2" t="n"/>
+      <c r="D78" s="2" t="n">
+        <v>27962000</v>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Ishonch Qurilish Materiallari MChJ</t>
+          <t>Andijon Non MChJ</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>357452192</t>
+          <t>379389285</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>20208000577393673001</t>
+          <t>20208000273400902001</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>АРЕНДНАЯ ПЛАТА ЗА АВГУСТ 2026 Г. ПО ДОГОВОРУ №45/22</t>
+          <t>Shartnoma №165/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>451511000</v>
+        <v>187912000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="B79" t="n">
         <v>171</v>
       </c>
       <c r="C79" s="2" t="n"/>
       <c r="D79" s="2" t="n">
-        <v>31269000</v>
+        <v>94326000</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Denov Metall MChJ</t>
+          <t>Farg'ona Qurilish MChJ</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>251039941</t>
+          <t>382544262</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20208000285274216001</t>
+          <t>20208000648973157001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3381,542 +3381,542 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №141/26 от 10.08.2026</t>
+          <t>Оплата за продукцию по договору №287/26, НДС 12%</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>482780000</v>
+        <v>282238000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="B80" t="n">
         <v>172</v>
       </c>
-      <c r="C80" s="2" t="n"/>
-      <c r="D80" s="2" t="n">
-        <v>10777000</v>
-      </c>
+      <c r="C80" s="2" t="n">
+        <v>9420000</v>
+      </c>
+      <c r="D80" s="2" t="n"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Yulduz Qurilish MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>218825442</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>20208000266489731001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №156/26, НС 12%</t>
+          <t>Социальный налог за июль 2026 г.</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>493557000</v>
+        <v>272818000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="B81" t="n">
         <v>173</v>
       </c>
       <c r="C81" s="2" t="n">
-        <v>409952000</v>
+        <v>9420000</v>
       </c>
       <c r="D81" s="2" t="n"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Bunyodkor Tikuv MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>294154199</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>20208000787835044001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №2837</t>
+          <t>Jismoniy shaxslar daromad solig'i iyul 2026</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>83605000</v>
+        <v>263398000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n">
-        <v>46246</v>
+        <v>46251</v>
       </c>
       <c r="B82" t="n">
         <v>174</v>
       </c>
-      <c r="C82" s="2" t="n"/>
-      <c r="D82" s="2" t="n">
-        <v>12359000</v>
-      </c>
+      <c r="C82" s="2" t="n">
+        <v>25404000</v>
+      </c>
+      <c r="D82" s="2" t="n"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sarbon Mebel MChJ</t>
+          <t>Namangan Non AJ</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>295815642</t>
+          <t>349743926</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20208000741618409001</t>
+          <t>20208000314942583001</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №225/26, НДС 12%</t>
+          <t>Оплата за сырье по договору №231/26 от 17.08.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>95964000</v>
+        <v>237994000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B83" t="n">
         <v>175</v>
       </c>
-      <c r="C83" s="2" t="n"/>
-      <c r="D83" s="2" t="n">
-        <v>89311000</v>
-      </c>
+      <c r="C83" s="2" t="n">
+        <v>46618000</v>
+      </c>
+      <c r="D83" s="2" t="n"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Yulduz Qurilish MChJ</t>
+          <t>Farg'ona Avto Savdo XK</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>218825442</t>
+          <t>225696010</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000266489731001</t>
+          <t>20208000364591236001</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №156/26 от 14.08.2026</t>
+          <t>ПРЕДОПЛАТА ЗА МАТЕРИАЛЫ ПО ДОГОВОРУ №42/26</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>185275000</v>
+        <v>191376000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="B84" t="n">
         <v>176</v>
       </c>
-      <c r="C84" s="2" t="n"/>
-      <c r="D84" s="2" t="n">
-        <v>25162000</v>
-      </c>
+      <c r="C84" s="2" t="n">
+        <v>248847000</v>
+      </c>
+      <c r="D84" s="2" t="n"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Yulduz Qurilish MChJ</t>
+          <t>Oltin Vodiy Yog'och XK</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>218825442</t>
+          <t>367002358</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>20208000266489731001</t>
+          <t>20208000047461089001</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №253/26 от 14.08.2026</t>
+          <t>Оплата за сырье подог. №226/26 от 18.08.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>210437000</v>
+        <v>-57471000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
-        <v>46248</v>
+        <v>46253</v>
       </c>
       <c r="B85" t="n">
         <v>177</v>
       </c>
       <c r="C85" s="2" t="n"/>
       <c r="D85" s="2" t="n">
-        <v>6044000</v>
+        <v>23621000</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Yulduz Qurilish MChJ</t>
+          <t>Farg'ona Qurilish MChJ</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>218825442</t>
+          <t>382544262</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>20208000266489731001</t>
+          <t>20208000648973157001</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №2936 за поставленный товар</t>
+          <t>Оплата за товар по счет-фактуре №2290 от 19.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>216481000</v>
+        <v>-33850000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="B86" t="n">
         <v>178</v>
       </c>
       <c r="C86" s="2" t="n"/>
       <c r="D86" s="2" t="n">
-        <v>16479000</v>
+        <v>13247000</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Yulduz Qurilish MChJ</t>
+          <t>Farg'ona Qurilish MChJ</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>218825442</t>
+          <t>382544262</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>20208000266489731001</t>
+          <t>20208000648973157001</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №7980 за поставленный товар</t>
+          <t>Tovar uchun to'lov, hisob-faktura №3782 19.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>232960000</v>
+        <v>-20603000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="B87" t="n">
         <v>179</v>
       </c>
-      <c r="C87" s="2" t="n"/>
-      <c r="D87" s="2" t="n">
-        <v>12622000</v>
-      </c>
+      <c r="C87" s="2" t="n">
+        <v>60895000</v>
+      </c>
+      <c r="D87" s="2" t="n"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Yulduz Qurilish MChJ</t>
+          <t>Namangan Non AJ</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>218825442</t>
+          <t>349743926</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>20208000266489731001</t>
+          <t>20208000314942583001</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №5797 за поставленный товар</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №33/26, QQS bilan</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>245582000</v>
+        <v>-81498000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n">
-        <v>46251</v>
+        <v>46255</v>
       </c>
       <c r="B88" t="n">
         <v>180</v>
       </c>
       <c r="C88" s="2" t="n"/>
       <c r="D88" s="2" t="n">
-        <v>11421000</v>
+        <v>15072000</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Yulduz Qurilish MChJ</t>
+          <t>Durdona Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>218825442</t>
+          <t>203994162</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>20208000266489731001</t>
+          <t>20208000527421691001</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №215/26 от 17.08.2026</t>
+          <t>Предоплата за товар по договору №242/26 от 21.08.2026</t>
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>257003000</v>
+        <v>-66426000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="B89" t="n">
         <v>181</v>
       </c>
       <c r="C89" s="2" t="n"/>
       <c r="D89" s="2" t="n">
-        <v>10364000</v>
+        <v>57178000</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Yulduz Qurilish MChJ</t>
+          <t>Barakali Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>218825442</t>
+          <t>215122171</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>20208000266489731001</t>
+          <t>20208000909268904001</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №157/26 от 17.08.2026</t>
+          <t>Предоплата за товар по договору №238/26 от 24.08.2026</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>267367000</v>
+        <v>-9248000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="B90" t="n">
         <v>182</v>
       </c>
       <c r="C90" s="2" t="n"/>
       <c r="D90" s="2" t="n">
-        <v>9474000</v>
+        <v>27663000</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Yulduz Qurilish MChJ</t>
+          <t>Farg'ona Qurilish MChJ</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>218825442</t>
+          <t>382544262</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20208000266489731001</t>
+          <t>20208000648973157001</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №112/26, НДС 12%</t>
+          <t>Оплата за продукцию по договору №218/26, НДС 12%</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>276841000</v>
+        <v>18415000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="B91" t="n">
         <v>183</v>
       </c>
-      <c r="C91" s="2" t="n"/>
-      <c r="D91" s="2" t="n">
-        <v>5419000</v>
-      </c>
+      <c r="C91" s="2" t="n">
+        <v>5283000</v>
+      </c>
+      <c r="D91" s="2" t="n"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Bahor Ip-Kalava MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>251151221</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20208000119092689001</t>
+          <t>20208000252939030001</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Shartnoma №133/26 bo'yicha oldindan to'lov</t>
+          <t>Elektr energiyasi uchun to'lov avgust</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>282260000</v>
+        <v>13132000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="B92" t="n">
         <v>184</v>
       </c>
       <c r="C92" s="2" t="n">
-        <v>9420000</v>
+        <v>13707000</v>
       </c>
       <c r="D92" s="2" t="n"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Namangan Non AJ</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>349743926</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000314942583001</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Уплата социального налога за июль</t>
+          <t>Предоплата за материалы по договору №208/26</t>
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>272840000</v>
+        <v>-575000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="B93" t="n">
         <v>185</v>
       </c>
       <c r="C93" s="2" t="n">
-        <v>9420000</v>
+        <v>14467000</v>
       </c>
       <c r="D93" s="2" t="n"/>
       <c r="E93" t="inlineStr">
@@ -3941,197 +3941,197 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Налог на доходы физических лиц за июль 2026 г.</t>
+          <t>Уплата налога на добавленную стоимость за июль</t>
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>263420000</v>
+        <v>-15042000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="B94" t="n">
         <v>186</v>
       </c>
       <c r="C94" s="2" t="n">
-        <v>27480000</v>
+        <v>16714000</v>
       </c>
       <c r="D94" s="2" t="n"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Denov Moy MChJ</t>
+          <t>Farg'ona Avto Savdo XK</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>398308345</t>
+          <t>225696010</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>20208000059555391001</t>
+          <t>20208000364591236001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №279/26</t>
+          <t>Оплата за упаковочные материалы, с/ф №2362</t>
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>235940000</v>
+        <v>-31756000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
-        <v>46253</v>
+        <v>46258</v>
       </c>
       <c r="B95" t="n">
         <v>187</v>
       </c>
-      <c r="C95" s="2" t="n"/>
-      <c r="D95" s="2" t="n">
-        <v>27800000</v>
-      </c>
+      <c r="C95" s="2" t="n">
+        <v>55999000</v>
+      </c>
+      <c r="D95" s="2" t="n"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Yulduz Qurilish MChJ</t>
+          <t>Farg'ona Avto Savdo XK</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>218825442</t>
+          <t>225696010</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>20208000266489731001</t>
+          <t>20208000364591236001</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №1826, НДС 12%</t>
+          <t>Оплата за сырье по дог. №237/26 от 24.08.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>263740000</v>
+        <v>-87755000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n">
-        <v>46253</v>
+        <v>46259</v>
       </c>
       <c r="B96" t="n">
         <v>188</v>
       </c>
       <c r="C96" s="2" t="n"/>
       <c r="D96" s="2" t="n">
-        <v>12362000</v>
+        <v>11878000</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Guliston Meva Eksport MChJ</t>
+          <t>Andijon Non MChJ</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>226793892</t>
+          <t>379389285</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>20208000572734009001</t>
+          <t>20208000273400902001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №167/26 от 19.08.2026</t>
+          <t>Оплата за продукцию по договору №43/26, НДС 12%</t>
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>276102000</v>
+        <v>-75877000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
-        <v>46254</v>
+        <v>46260</v>
       </c>
       <c r="B97" t="n">
         <v>189</v>
       </c>
-      <c r="C97" s="2" t="n"/>
-      <c r="D97" s="2" t="n">
-        <v>112248000</v>
-      </c>
+      <c r="C97" s="2" t="n">
+        <v>41144000</v>
+      </c>
+      <c r="D97" s="2" t="n"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Guliston Meva Eksport MChJ</t>
+          <t>Namangan Non AJ</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>226793892</t>
+          <t>349743926</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>20208000572734009001</t>
+          <t>20208000314942583001</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №2856 от 20.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за транспортные услуги по договору №261/26</t>
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>388350000</v>
+        <v>-117021000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n">
-        <v>46254</v>
+        <v>46261</v>
       </c>
       <c r="B98" t="n">
         <v>190</v>
       </c>
       <c r="C98" s="2" t="n"/>
       <c r="D98" s="2" t="n">
-        <v>10330000</v>
+        <v>195742000</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Andijon Qurilish MChJ</t>
+          <t>Farg'ona Qurilish MChJ</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>366670023</t>
+          <t>382544262</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>20208000800474610001</t>
+          <t>20208000648973157001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4141,277 +4141,272 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №8718 за поставленный товар</t>
+          <t>Mahsulot uchun to'lov, shartnoma №108/26, QQ 12%</t>
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>398680000</v>
+        <v>78721000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
-        <v>46254</v>
+        <v>46265</v>
       </c>
       <c r="B99" t="n">
         <v>191</v>
       </c>
-      <c r="C99" s="2" t="n">
-        <v>114538000</v>
-      </c>
-      <c r="D99" s="2" t="n"/>
+      <c r="C99" s="2" t="n"/>
+      <c r="D99" s="2" t="n">
+        <v>408580000</v>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Namangan Qurilish Materiallari MChJ</t>
+          <t>Farg'ona Qurilish MChJ</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>274282313</t>
+          <t>382544262</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>20208000428330222001</t>
+          <t>20208000648973157001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №200/26</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №5568</t>
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>284142000</v>
+        <v>487301000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="B100" t="n">
         <v>192</v>
       </c>
       <c r="C100" s="2" t="n"/>
       <c r="D100" s="2" t="n">
-        <v>12758000</v>
+        <v>39454000</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Guliston Meva Eksport MChJ</t>
+          <t>Farg'ona Qurilish MChJ</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>226793892</t>
+          <t>382544262</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000572734009001</t>
+          <t>20208000648973157001</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Shartnoma №96/26 bo'yicha olindan to'lov</t>
+          <t>Предоплата за товар по договору №134/26 от 31.08.2026</t>
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>296900000</v>
+        <v>526755000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="B101" t="n">
         <v>193</v>
       </c>
-      <c r="C101" s="2" t="n">
-        <v>13706000</v>
-      </c>
-      <c r="D101" s="2" t="n"/>
+      <c r="C101" s="2" t="n"/>
+      <c r="D101" s="2" t="n">
+        <v>39139000</v>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Andijon Non MChJ</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>379389285</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000273400902001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>QQS iyul 2026 uchun</t>
+          <t>Предоплата за товар по договору №28/26 от 31.08.2026</t>
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>283194000</v>
+        <v>565894000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="B102" t="n">
         <v>194</v>
       </c>
-      <c r="C102" s="2" t="n">
-        <v>21263000</v>
-      </c>
-      <c r="D102" s="2" t="n"/>
+      <c r="C102" s="2" t="n"/>
+      <c r="D102" s="2" t="n">
+        <v>36342000</v>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Namangan Qurilish Materiallari MChJ</t>
+          <t>Farg'ona Qurilish MChJ</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>274282313</t>
+          <t>382544262</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20208000428330222001</t>
+          <t>20208000648973157001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №1252</t>
+          <t>Оплата по счет-фактуре №2048 за поставленный товар</t>
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>261931000</v>
+        <v>602236000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="B103" t="n">
         <v>195</v>
       </c>
-      <c r="C103" s="2" t="n">
-        <v>32742000</v>
-      </c>
-      <c r="D103" s="2" t="n"/>
+      <c r="C103" s="2" t="n"/>
+      <c r="D103" s="2" t="n">
+        <v>22716000</v>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Oqtosh Logistik MChJ</t>
+          <t>Andijon Non MChJ</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>293903073</t>
+          <t>379389285</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>20208000103408145001</t>
+          <t>20208000273400902001</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №6802</t>
+          <t>Оплата за товар по счет-фактуре №8111 от 31.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>229189000</v>
+        <v>624952000</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="B104" t="n">
         <v>196</v>
       </c>
       <c r="C104" s="2" t="n">
-        <v>57837000</v>
+        <v>300000</v>
       </c>
       <c r="D104" s="2" t="n"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Bunyodkor Tikuv MChJ</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>294154199</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>20208000787835044001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно с/ф №9230</t>
+          <t>Bank xizmati uchun komissiya</t>
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>171352000</v>
+        <v>624652000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="B105" t="n">
         <v>197</v>
       </c>
       <c r="C105" s="2" t="n">
-        <v>64959000</v>
+        <v>14648000</v>
       </c>
       <c r="D105" s="2" t="n"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Namangan Qurilish Materiallari MChJ</t>
+          <t>Toshkent Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>274282313</t>
+          <t>304206857</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000428330222001</t>
+          <t>20208000071377990001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -4421,641 +4416,641 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по дог. №165/26</t>
+          <t>Предоплата за материалы по договору №73/26</t>
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>106393000</v>
+        <v>610004000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n">
-        <v>46259</v>
+        <v>46265</v>
       </c>
       <c r="B106" t="n">
         <v>198</v>
       </c>
-      <c r="C106" s="2" t="n"/>
-      <c r="D106" s="2" t="n">
-        <v>16581000</v>
-      </c>
+      <c r="C106" s="2" t="n">
+        <v>30733000</v>
+      </c>
+      <c r="D106" s="2" t="n"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Zafar Farm Savdo MChJ</t>
+          <t>Namangan Non AJ</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>287497439</t>
+          <t>349743926</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>20208000643149425001</t>
+          <t>20208000314942583001</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №244/26, QQS 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartnma №2/26</t>
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>122974000</v>
+        <v>579271000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="n">
-        <v>46259</v>
+        <v>46265</v>
       </c>
       <c r="B107" t="n">
         <v>199</v>
       </c>
       <c r="C107" s="2" t="n">
-        <v>5283000</v>
+        <v>39680000</v>
       </c>
       <c r="D107" s="2" t="n"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Namangan Non AJ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>349743926</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>20208000909446486001</t>
+          <t>20208000314942583001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию за август 2026 г.</t>
+          <t>Предоплата за материалы по договору №259/26</t>
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>117691000</v>
+        <v>539591000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="n">
-        <v>46259</v>
+        <v>46265</v>
       </c>
       <c r="B108" t="n">
         <v>200</v>
       </c>
       <c r="C108" s="2" t="n">
-        <v>19575000</v>
+        <v>122436000</v>
       </c>
       <c r="D108" s="2" t="n"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Denov Moy MChJ</t>
+          <t>Namangan Non AJ</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>398308345</t>
+          <t>349743926</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>20208000059555391001</t>
+          <t>20208000314942583001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №8684</t>
+          <t>Оплата за транспортные услуги по договору №287/26</t>
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>98116000</v>
+        <v>417155000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="n">
-        <v>46260</v>
+        <v>46266</v>
       </c>
       <c r="B109" t="n">
         <v>201</v>
       </c>
       <c r="C109" s="2" t="n"/>
       <c r="D109" s="2" t="n">
-        <v>186419000</v>
+        <v>7441000</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Bahor Ip-Kalava MChJ</t>
+          <t>Farg'ona Qurilish MChJ</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>251151221</t>
+          <t>382544262</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>20208000119092689001</t>
+          <t>20208000648973157001</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №55/26 от 26.08.2026</t>
+          <t>Предоплата за товар по договору №71/26 от 01.09.2026</t>
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>284535000</v>
+        <v>424596000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="n">
-        <v>46261</v>
+        <v>46267</v>
       </c>
       <c r="B110" t="n">
         <v>202</v>
       </c>
-      <c r="C110" s="2" t="n">
-        <v>32541000</v>
-      </c>
-      <c r="D110" s="2" t="n"/>
+      <c r="C110" s="2" t="n"/>
+      <c r="D110" s="2" t="n">
+        <v>6622000</v>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Namangan Qurilish Materiallari MChJ</t>
+          <t>Farg'ona Qurilish MChJ</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>274282313</t>
+          <t>382544262</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>20208000428330222001</t>
+          <t>20208000648973157001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №7856</t>
+          <t>Оплата за продукцию по договору №187/26, НДС 12%</t>
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>251994000</v>
+        <v>431218000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="n">
-        <v>46262</v>
+        <v>46268</v>
       </c>
       <c r="B111" t="n">
         <v>203</v>
       </c>
-      <c r="C111" s="2" t="n"/>
-      <c r="D111" s="2" t="n">
-        <v>55251000</v>
-      </c>
+      <c r="C111" s="2" t="n">
+        <v>40550000</v>
+      </c>
+      <c r="D111" s="2" t="n"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Oydin Farm Savdo MChJ</t>
+          <t>Oltin Vodiy Yog'och XK</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>308042068</t>
+          <t>367002358</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>20208000720713779001</t>
+          <t>20208000047461089001</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Shartnoma №174/26 bo'yicha oldindan to'lov</t>
+          <t>ОПЛАТА ЗА СЫРЬЕ ПО ДОГОВОРУ №219/26 ОТ 03.09.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>307245000</v>
+        <v>390668000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="n">
-        <v>46262</v>
+        <v>46268</v>
       </c>
       <c r="B112" t="n">
         <v>204</v>
       </c>
-      <c r="C112" s="2" t="n"/>
-      <c r="D112" s="2" t="n">
-        <v>9894000</v>
-      </c>
+      <c r="C112" s="2" t="n">
+        <v>275918000</v>
+      </c>
+      <c r="D112" s="2" t="n"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Bahor Ip-Kalava MChJ</t>
+          <t>Farg'ona Avto Savdo XK</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>251151221</t>
+          <t>225696010</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>20208000119092689001</t>
+          <t>20208000364591236001</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. 234/26, НДС 12%</t>
+          <t>Оплата за товары согласно счет-фактуре №7034</t>
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>317139000</v>
+        <v>114750000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="n">
-        <v>46262</v>
+        <v>46269</v>
       </c>
       <c r="B113" t="n">
         <v>205</v>
       </c>
       <c r="C113" s="2" t="n"/>
       <c r="D113" s="2" t="n">
-        <v>5413000</v>
+        <v>11976000</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Sarbon Mebel MChJ</t>
+          <t>Barakali Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>295815642</t>
+          <t>215122171</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20208000741618409001</t>
+          <t>20208000909268904001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №6953 за поставленный товар</t>
+          <t>Shartnoma №69/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>322552000</v>
+        <v>126726000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="n">
-        <v>46265</v>
+        <v>46269</v>
       </c>
       <c r="B114" t="n">
         <v>206</v>
       </c>
-      <c r="C114" s="2" t="n"/>
-      <c r="D114" s="2" t="n">
-        <v>26089000</v>
-      </c>
+      <c r="C114" s="2" t="n">
+        <v>71150000</v>
+      </c>
+      <c r="D114" s="2" t="n"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Yulduz Qurilish MChJ</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>218825442</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>20208000266489731001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №45/26, НДС 12%</t>
+          <t>Перечисление заработной платы за август 2026 г. согласно реестру №8254</t>
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>348641000</v>
+        <v>55576000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="n">
-        <v>46265</v>
+        <v>46270</v>
       </c>
       <c r="B115" t="n">
         <v>207</v>
       </c>
-      <c r="C115" s="2" t="n"/>
-      <c r="D115" s="2" t="n">
-        <v>18001000</v>
-      </c>
+      <c r="C115" s="2" t="n">
+        <v>68500000</v>
+      </c>
+      <c r="D115" s="2" t="n"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Guliston Meva Eksport MChJ</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>226793892</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-9502)</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>20208000572734009001</t>
+          <t>16307000215835234417</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №61/26, НДС 12%</t>
+          <t>Kredit shartnomasi L-2025-9502 bo'yicha navbatdagi to'lov (09.2026)</t>
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>366642000</v>
+        <v>-12924000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="n">
-        <v>46265</v>
+        <v>46272</v>
       </c>
       <c r="B116" t="n">
         <v>208</v>
       </c>
       <c r="C116" s="2" t="n"/>
       <c r="D116" s="2" t="n">
-        <v>6877000</v>
+        <v>201315000</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Yulduz Qurilish MChJ</t>
+          <t>Farg'ona Qurilish MChJ</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>218825442</t>
+          <t>382544262</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20208000266489731001</t>
+          <t>20208000648973157001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №8/26 от 31.08.2026</t>
+          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №4482 ОТ 07.09.2026, В Т.Ч. НДС 12%</t>
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>373519000</v>
+        <v>188391000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="n">
-        <v>46265</v>
+        <v>46272</v>
       </c>
       <c r="B117" t="n">
         <v>209</v>
       </c>
       <c r="C117" s="2" t="n"/>
       <c r="D117" s="2" t="n">
-        <v>5735000</v>
+        <v>28032000</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Yulduz Qurilish MChJ</t>
+          <t>Farg'ona Qurilish MChJ</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>218825442</t>
+          <t>382544262</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20208000266489731001</t>
+          <t>20208000648973157001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №262/26, НДС 12%</t>
+          <t>Оплата по с/ф №1658 за поставленный товар</t>
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>379254000</v>
+        <v>216423000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="n">
-        <v>46265</v>
+        <v>46272</v>
       </c>
       <c r="B118" t="n">
         <v>210</v>
       </c>
-      <c r="C118" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D118" s="2" t="n"/>
+      <c r="C118" s="2" t="n"/>
+      <c r="D118" s="2" t="n">
+        <v>13056000</v>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Farg'ona Qurilish MChJ</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>382544262</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000648973157001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Комиссия за перевод</t>
+          <t>Оплата за товар по счет-фактуре №1244 от 07.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>378954000</v>
+        <v>229479000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="n">
-        <v>46268</v>
+        <v>46272</v>
       </c>
       <c r="B119" t="n">
         <v>211</v>
       </c>
-      <c r="C119" s="2" t="n">
-        <v>48404000</v>
-      </c>
-      <c r="D119" s="2" t="n"/>
+      <c r="C119" s="2" t="n"/>
+      <c r="D119" s="2" t="n">
+        <v>11179000</v>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Bunyodkor Tikuv MChJ</t>
+          <t>Farg'ona Qurilish MChJ</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>294154199</t>
+          <t>382544262</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000787835044001</t>
+          <t>20208000648973157001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №103/26 от 03.09.2026, НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №6869</t>
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>330550000</v>
+        <v>240658000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="n">
-        <v>46268</v>
+        <v>46272</v>
       </c>
       <c r="B120" t="n">
         <v>212</v>
       </c>
-      <c r="C120" s="2" t="n">
-        <v>313977000</v>
-      </c>
-      <c r="D120" s="2" t="n"/>
+      <c r="C120" s="2" t="n"/>
+      <c r="D120" s="2" t="n">
+        <v>10009000</v>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Denov Moy MChJ</t>
+          <t>Farg'ona Qurilish MChJ</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>398308345</t>
+          <t>382544262</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>20208000059555391001</t>
+          <t>20208000648973157001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>TOVARLAR UCHUN TO'LOV H/F №9838</t>
+          <t>Оплата за товар по счет-фактуре №3220 от 07.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>16573000</v>
+        <v>250667000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="n">
-        <v>46270</v>
+        <v>46272</v>
       </c>
       <c r="B121" t="n">
         <v>213</v>
       </c>
-      <c r="C121" s="2" t="n">
-        <v>68500000</v>
-      </c>
-      <c r="D121" s="2" t="n"/>
+      <c r="C121" s="2" t="n"/>
+      <c r="D121" s="2" t="n">
+        <v>6629000</v>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-9502)</t>
+          <t>Farg'ona Qurilish MChJ</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>382544262</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>16307000215835234417</t>
+          <t>20208000648973157001</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-9502 bo'yicha navbatdagi to'lov (09.2026)</t>
+          <t>Оплата по счет-фактуре №8741 за поставленный товар</t>
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>-51927000</v>
+        <v>257296000</v>
       </c>
     </row>
     <row r="122">
@@ -5066,151 +5061,156 @@
         <v>214</v>
       </c>
       <c r="C122" s="2" t="n">
-        <v>24037000</v>
+        <v>61198000</v>
       </c>
       <c r="D122" s="2" t="n"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Oqtosh Logistik MChJ</t>
+          <t>Farg'ona Avto Savdo XK</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>293903073</t>
+          <t>225696010</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20208000103408145001</t>
+          <t>20208000364591236001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №7441</t>
+          <t>Tovarlar uchun to'lov h/f №5203</t>
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>-75964000</v>
+        <v>196098000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B123" t="n">
         <v>215</v>
       </c>
-      <c r="C123" s="2" t="n">
-        <v>71150000</v>
-      </c>
-      <c r="D123" s="2" t="n"/>
+      <c r="C123" s="2" t="n"/>
+      <c r="D123" s="2" t="n">
+        <v>32521000</v>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Farg'ona Qurilish MChJ</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>382544262</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000648973157001</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Заработная плата за август 2026 г. (перечисление на пластиковые карты)</t>
+          <t>Оплата за продукцию по дог. №30/26, НДС 12%</t>
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>-147114000</v>
+        <v>228619000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B124" t="n">
         <v>216</v>
       </c>
-      <c r="C124" s="2" t="n">
-        <v>135379000</v>
-      </c>
-      <c r="D124" s="2" t="n"/>
+      <c r="C124" s="2" t="n"/>
+      <c r="D124" s="2" t="n">
+        <v>25047000</v>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Bunyodkor Tikuv MChJ</t>
+          <t>Ishonch Non AJ</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>294154199</t>
+          <t>381564267</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>20208000787835044001</t>
+          <t>20208000161840949001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №5089</t>
+          <t>Yetkazilgantovar uchun to'lov h/f №1925</t>
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>-282493000</v>
+        <v>253666000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B125" t="n">
         <v>217</v>
       </c>
-      <c r="C125" s="2" t="n">
-        <v>162552000</v>
-      </c>
-      <c r="D125" s="2" t="n"/>
+      <c r="C125" s="2" t="n"/>
+      <c r="D125" s="2" t="n">
+        <v>18297000</v>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Bunyodkor Tikuv MChJ</t>
+          <t>Farg'ona Qurilish MChJ</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>294154199</t>
+          <t>382544262</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>20208000787835044001</t>
+          <t>20208000648973157001</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №4736</t>
+          <t>Оплата по счет-фактуре №8120 за поставленный товар</t>
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>-445045000</v>
+        <v>271963000</v>
       </c>
     </row>
     <row r="126">
@@ -5220,37 +5220,37 @@
       <c r="B126" t="n">
         <v>218</v>
       </c>
-      <c r="C126" s="2" t="n"/>
-      <c r="D126" s="2" t="n">
-        <v>207897000</v>
-      </c>
+      <c r="C126" s="2" t="n">
+        <v>8706000</v>
+      </c>
+      <c r="D126" s="2" t="n"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Yulduz Qurilish MChJ</t>
+          <t>Qarshi Qurilish MChJ</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>218825442</t>
+          <t>342823132</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>20208000266489731001</t>
+          <t>20208000283302227001</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №14/26, НДС 12%</t>
+          <t>Ijara haqi sentyabr oyi uchun, shartnoma №94/21</t>
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>-237148000</v>
+        <v>263257000</v>
       </c>
     </row>
     <row r="127">
@@ -5261,102 +5261,102 @@
         <v>219</v>
       </c>
       <c r="C127" s="2" t="n">
-        <v>24184000</v>
+        <v>30438000</v>
       </c>
       <c r="D127" s="2" t="n"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Oqtosh Logistik MChJ</t>
+          <t>Namangan Non AJ</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>293903073</t>
+          <t>349743926</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>20208000103408145001</t>
+          <t>20208000314942583001</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №6702</t>
+          <t>Оплата за сырье по дог. №244/26 от 08.09.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>-261332000</v>
+        <v>232819000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B128" t="n">
         <v>220</v>
       </c>
       <c r="C128" s="2" t="n"/>
       <c r="D128" s="2" t="n">
-        <v>29117000</v>
+        <v>9668000</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Yulduz Qurilish MChJ</t>
+          <t>Durdona Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>218825442</t>
+          <t>203994162</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>20208000266489731001</t>
+          <t>20208000527421691001</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №287/26, НДС 12%</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №94/26, НДС 12%</t>
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>-232215000</v>
+        <v>242487000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="n">
-        <v>46274</v>
+        <v>46279</v>
       </c>
       <c r="B129" t="n">
         <v>221</v>
       </c>
-      <c r="C129" s="2" t="n">
-        <v>8706000</v>
-      </c>
-      <c r="D129" s="2" t="n"/>
+      <c r="C129" s="2" t="n"/>
+      <c r="D129" s="2" t="n">
+        <v>29566000</v>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Ishonch Qurilish Materiallari MChJ</t>
+          <t>Farg'ona Qurilish MChJ</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>357452192</t>
+          <t>382544262</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>20208000577393673001</t>
+          <t>20208000648973157001</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -5366,451 +5366,451 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Ijara haqi sentyabr oyi uchun, shartnoma №45/22</t>
+          <t>Оплата за товар по счет-фактуре №717 от 14.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>-240921000</v>
+        <v>272053000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="3" t="n">
-        <v>46274</v>
+        <v>46279</v>
       </c>
       <c r="B130" t="n">
         <v>222</v>
       </c>
-      <c r="C130" s="2" t="n">
-        <v>13733000</v>
-      </c>
-      <c r="D130" s="2" t="n"/>
+      <c r="C130" s="2" t="n"/>
+      <c r="D130" s="2" t="n">
+        <v>5996000</v>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Denov Moy MChJ</t>
+          <t>Barakali Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>398308345</t>
+          <t>215122171</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20208000059555391001</t>
+          <t>20208000909268904001</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №286/26 от 09.09.2026, НДС 12%</t>
+          <t>Предоплата за товар по договору №26/26 от 14.09.2026</t>
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>-254654000</v>
+        <v>278049000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="n">
-        <v>46275</v>
+        <v>46279</v>
       </c>
       <c r="B131" t="n">
         <v>223</v>
       </c>
-      <c r="C131" s="2" t="n"/>
-      <c r="D131" s="2" t="n">
-        <v>104668000</v>
-      </c>
+      <c r="C131" s="2" t="n">
+        <v>9702000</v>
+      </c>
+      <c r="D131" s="2" t="n"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Yulduz Qurilish MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>218825442</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>20208000266489731001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №5242 от 10.09.2026, в т.ч. НДС 12%</t>
+          <t>Уплата социального налога за август</t>
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>-149986000</v>
+        <v>268347000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="3" t="n">
-        <v>46275</v>
+        <v>46279</v>
       </c>
       <c r="B132" t="n">
         <v>224</v>
       </c>
-      <c r="C132" s="2" t="n"/>
-      <c r="D132" s="2" t="n">
-        <v>36329000</v>
-      </c>
+      <c r="C132" s="2" t="n">
+        <v>9702000</v>
+      </c>
+      <c r="D132" s="2" t="n"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Yulduz Qurilish MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>218825442</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>20208000266489731001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №134/26, QQS 12%</t>
+          <t>НДФЛ за август 2026</t>
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>-113657000</v>
+        <v>258645000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="3" t="n">
-        <v>46275</v>
+        <v>46279</v>
       </c>
       <c r="B133" t="n">
         <v>225</v>
       </c>
-      <c r="C133" s="2" t="n"/>
-      <c r="D133" s="2" t="n">
-        <v>16106000</v>
-      </c>
+      <c r="C133" s="2" t="n">
+        <v>25059000</v>
+      </c>
+      <c r="D133" s="2" t="n"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Yulduz Qurilish MChJ</t>
+          <t>Farg'ona Avto Savdo XK</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>218825442</t>
+          <t>225696010</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>20208000266489731001</t>
+          <t>20208000364591236001</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №57/26 от 10.09.2026</t>
+          <t>Оплата за упаковочные материалы, с/ф №4333</t>
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>-97551000</v>
+        <v>233586000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="3" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B134" t="n">
         <v>226</v>
       </c>
       <c r="C134" s="2" t="n">
-        <v>14488000</v>
+        <v>40361000</v>
       </c>
       <c r="D134" s="2" t="n"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Bunyodkor Tikuv MChJ</t>
+          <t>Farg'ona Avto Savdo XK</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>294154199</t>
+          <t>225696010</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>20208000787835044001</t>
+          <t>20208000364591236001</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №9654</t>
+          <t>Предоплата за материалы по договору №186/26</t>
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>-112039000</v>
+        <v>193225000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="3" t="n">
-        <v>46279</v>
+        <v>46281</v>
       </c>
       <c r="B135" t="n">
         <v>227</v>
       </c>
-      <c r="C135" s="2" t="n">
-        <v>58075000</v>
-      </c>
-      <c r="D135" s="2" t="n"/>
+      <c r="C135" s="2" t="n"/>
+      <c r="D135" s="2" t="n">
+        <v>8142000</v>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Denov Moy MChJ</t>
+          <t>Farg'ona Qurilish MChJ</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>398308345</t>
+          <t>382544262</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>20208000059555391001</t>
+          <t>20208000648973157001</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №8078</t>
+          <t>Оплата за продукцию по дог. №259/26, НДС 12%</t>
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>-170114000</v>
+        <v>201367000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="3" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B136" t="n">
         <v>228</v>
       </c>
-      <c r="C136" s="2" t="n">
-        <v>9702000</v>
-      </c>
-      <c r="D136" s="2" t="n"/>
+      <c r="C136" s="2" t="n"/>
+      <c r="D136" s="2" t="n">
+        <v>31055000</v>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Ishonch Non AJ</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>381564267</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000161840949001</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Социальный налог за август 2026 г.</t>
+          <t>Оплата за продукцию по договору №114/26, НДС 12%</t>
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>-179816000</v>
+        <v>232422000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="3" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="B137" t="n">
         <v>229</v>
       </c>
-      <c r="C137" s="2" t="n">
-        <v>9702000</v>
-      </c>
-      <c r="D137" s="2" t="n"/>
+      <c r="C137" s="2" t="n"/>
+      <c r="D137" s="2" t="n">
+        <v>40498000</v>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Farg'ona Qurilish MChJ</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>382544262</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000648973157001</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Налог на доходы физических лиц за август 2026 г.</t>
+          <t>Оплата по счет-фактуре №5815 за поставленный товар</t>
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>-189518000</v>
+        <v>272920000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="3" t="n">
-        <v>46281</v>
+        <v>46286</v>
       </c>
       <c r="B138" t="n">
         <v>230</v>
       </c>
-      <c r="C138" s="2" t="n">
-        <v>49424000</v>
-      </c>
-      <c r="D138" s="2" t="n"/>
+      <c r="C138" s="2" t="n"/>
+      <c r="D138" s="2" t="n">
+        <v>86451000</v>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Oqtosh Logistik MChJ</t>
+          <t>Andijon Non MChJ</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>293903073</t>
+          <t>379389285</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>20208000103408145001</t>
+          <t>20208000273400902001</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №7323</t>
+          <t>Оплата за товар по счет-фактуре №2488 от 21.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>-238942000</v>
+        <v>359371000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B139" t="n">
         <v>231</v>
       </c>
-      <c r="C139" s="2" t="n">
-        <v>41837000</v>
-      </c>
-      <c r="D139" s="2" t="n"/>
+      <c r="C139" s="2" t="n"/>
+      <c r="D139" s="2" t="n">
+        <v>14894000</v>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Namangan Qurilish Materiallari MChJ</t>
+          <t>Barakali Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>274282313</t>
+          <t>345539163</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>20208000428330222001</t>
+          <t>20208000015951773001</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №9396</t>
+          <t>Оплата за товар по счет-фактуре №4604 от 21.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>-280779000</v>
+        <v>374265000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="3" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B140" t="n">
         <v>232</v>
       </c>
-      <c r="C140" s="2" t="n">
-        <v>78145000</v>
-      </c>
-      <c r="D140" s="2" t="n"/>
+      <c r="C140" s="2" t="n"/>
+      <c r="D140" s="2" t="n">
+        <v>10992000</v>
+      </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Oqtosh Logistik MChJ</t>
+          <t>Farg'ona Qurilish MChJ</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>293903073</t>
+          <t>382544262</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>20208000103408145001</t>
+          <t>20208000648973157001</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №209/26</t>
+          <t>Оплата по счет-фактуре №1904 за поставленный товар</t>
         </is>
       </c>
       <c r="J140" s="2" t="n">
-        <v>-358924000</v>
+        <v>385257000</v>
       </c>
     </row>
     <row r="141">
@@ -5822,35 +5822,35 @@
       </c>
       <c r="C141" s="2" t="n"/>
       <c r="D141" s="2" t="n">
-        <v>264880000</v>
+        <v>10046000</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Zafar Farm Savdo MChJ</t>
+          <t>Bog'ishamol Polimer MChJ</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>287497439</t>
+          <t>333661320</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>20208000643149425001</t>
+          <t>20208000165723716001</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №138/26, QQS 12%</t>
+          <t>Предоплата за товар по договору №36/26 от 21.09.2026</t>
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>-94044000</v>
+        <v>395303000</v>
       </c>
     </row>
     <row r="142">
@@ -5862,21 +5862,21 @@
       </c>
       <c r="C142" s="2" t="n"/>
       <c r="D142" s="2" t="n">
-        <v>17394000</v>
+        <v>5803000</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Yulduz Qurilish MChJ</t>
+          <t>Barakali Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>218825442</t>
+          <t>345539163</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>20208000266489731001</t>
+          <t>20208000015951773001</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -5886,11 +5886,11 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №236/26, НДС 12%</t>
+          <t>Shartnoma №238/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>-76650000</v>
+        <v>401106000</v>
       </c>
     </row>
     <row r="143">
@@ -5900,23 +5900,23 @@
       <c r="B143" t="n">
         <v>235</v>
       </c>
-      <c r="C143" s="2" t="n"/>
-      <c r="D143" s="2" t="n">
-        <v>12890000</v>
-      </c>
+      <c r="C143" s="2" t="n">
+        <v>27120000</v>
+      </c>
+      <c r="D143" s="2" t="n"/>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Yulduz Qurilish MChJ</t>
+          <t>Afrosiyob Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>218825442</t>
+          <t>353917886</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>20208000266489731001</t>
+          <t>20208000861700936001</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -5926,51 +5926,51 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Shartnoma №97/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за материалы по договору №142/26</t>
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>-63760000</v>
+        <v>373986000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="3" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B144" t="n">
         <v>236</v>
       </c>
-      <c r="C144" s="2" t="n">
-        <v>14420000</v>
-      </c>
-      <c r="D144" s="2" t="n"/>
+      <c r="C144" s="2" t="n"/>
+      <c r="D144" s="2" t="n">
+        <v>66570000</v>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Barakali Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>345539163</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000015951773001</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Уплата налога на добавленную стоимость за август</t>
+          <t>Оплата за продукцию по договору №65/26, НДС 12%</t>
         </is>
       </c>
       <c r="J144" s="2" t="n">
-        <v>-78180000</v>
+        <v>440556000</v>
       </c>
     </row>
     <row r="145">
@@ -5982,61 +5982,61 @@
       </c>
       <c r="C145" s="2" t="n"/>
       <c r="D145" s="2" t="n">
-        <v>52213000</v>
+        <v>9625000</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Yulduz Qurilish MChJ</t>
+          <t>Farg'ona Qurilish MChJ</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>218825442</t>
+          <t>382544262</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>20208000266489731001</t>
+          <t>20208000648973157001</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №1542 22.09.2026, QQS bilan</t>
+          <t>Предоплата за товар по договору №29/26 от 22.09.2026</t>
         </is>
       </c>
       <c r="J145" s="2" t="n">
-        <v>-25967000</v>
+        <v>450181000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="3" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B146" t="n">
         <v>238</v>
       </c>
       <c r="C146" s="2" t="n">
-        <v>5441000</v>
+        <v>24037000</v>
       </c>
       <c r="D146" s="2" t="n"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Afrosiyob Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>353917886</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>20208000909446486001</t>
+          <t>20208000861700936001</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -6046,37 +6046,37 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov sentyabr</t>
+          <t>Оплата за транспортные услуги по дог. №220/26</t>
         </is>
       </c>
       <c r="J146" s="2" t="n">
-        <v>-31408000</v>
+        <v>426144000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="3" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B147" t="n">
         <v>239</v>
       </c>
       <c r="C147" s="2" t="n"/>
       <c r="D147" s="2" t="n">
-        <v>23687000</v>
+        <v>48942000</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Bahor Ip-Kalava MChJ</t>
+          <t>Andijon Non MChJ</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>251151221</t>
+          <t>379389285</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>20208000119092689001</t>
+          <t>20208000273400902001</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -6086,311 +6086,831 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №235/26, НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №5845 от 23.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J147" s="2" t="n">
-        <v>-7721000</v>
+        <v>475086000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="3" t="n">
-        <v>46290</v>
+        <v>46288</v>
       </c>
       <c r="B148" t="n">
         <v>240</v>
       </c>
       <c r="C148" s="2" t="n"/>
       <c r="D148" s="2" t="n">
-        <v>77384000</v>
+        <v>31376000</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Yulduz Qurilish MChJ</t>
+          <t>Farg'ona Qurilish MChJ</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>218825442</t>
+          <t>382544262</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>20208000266489731001</t>
+          <t>20208000648973157001</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №59/26, НДС 12%</t>
+          <t>Предоплата за товар по договору №236/26 от 23.09.2026</t>
         </is>
       </c>
       <c r="J148" s="2" t="n">
-        <v>69663000</v>
+        <v>506462000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="3" t="n">
-        <v>46293</v>
+        <v>46288</v>
       </c>
       <c r="B149" t="n">
         <v>241</v>
       </c>
       <c r="C149" s="2" t="n"/>
       <c r="D149" s="2" t="n">
-        <v>185284000</v>
+        <v>24290000</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Sarbon Mebel MChJ</t>
+          <t>Farg'ona Qurilish MChJ</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>295815642</t>
+          <t>382544262</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>20208000741618409001</t>
+          <t>20208000648973157001</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №9943 от 28.09.2026, в т.ч. НДС 12%</t>
+          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №466 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
         </is>
       </c>
       <c r="J149" s="2" t="n">
-        <v>254947000</v>
+        <v>530752000</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="3" t="n">
-        <v>46293</v>
+        <v>46288</v>
       </c>
       <c r="B150" t="n">
         <v>242</v>
       </c>
       <c r="C150" s="2" t="n"/>
       <c r="D150" s="2" t="n">
-        <v>40593000</v>
+        <v>15698000</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Yulduz Qurilish MChJ</t>
+          <t>Farg'ona Qurilish MChJ</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>218825442</t>
+          <t>382544262</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>20208000266489731001</t>
+          <t>20208000648973157001</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №1636 за поставленный товар</t>
+          <t>Оплата за товар по счет-фактуре №9597 от 23.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J150" s="2" t="n">
-        <v>295540000</v>
+        <v>546450000</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="3" t="n">
-        <v>46293</v>
+        <v>46288</v>
       </c>
       <c r="B151" t="n">
         <v>243</v>
       </c>
-      <c r="C151" s="2" t="n"/>
-      <c r="D151" s="2" t="n">
-        <v>15310000</v>
-      </c>
+      <c r="C151" s="2" t="n">
+        <v>14238000</v>
+      </c>
+      <c r="D151" s="2" t="n"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Yulduz Qurilish MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>218825442</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>20208000266489731001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №154/26, НДС 12%</t>
+          <t>Уплата налога на добавленную стоимость за август</t>
         </is>
       </c>
       <c r="J151" s="2" t="n">
-        <v>310850000</v>
+        <v>532212000</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="3" t="n">
-        <v>46295</v>
+        <v>46288</v>
       </c>
       <c r="B152" t="n">
         <v>244</v>
       </c>
-      <c r="C152" s="2" t="n"/>
-      <c r="D152" s="2" t="n">
-        <v>117892000</v>
-      </c>
+      <c r="C152" s="2" t="n">
+        <v>219029000</v>
+      </c>
+      <c r="D152" s="2" t="n"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Guliston Meva Eksport MChJ</t>
+          <t>Namangan Non AJ</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>226793892</t>
+          <t>349743926</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>20208000572734009001</t>
+          <t>20208000314942583001</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Shartnoma №75/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за сырье по договору №148/26 от 23.09.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J152" s="2" t="n">
-        <v>428742000</v>
+        <v>313183000</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="3" t="n">
-        <v>46295</v>
+        <v>46289</v>
       </c>
       <c r="B153" t="n">
         <v>245</v>
       </c>
-      <c r="C153" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D153" s="2" t="n"/>
+      <c r="C153" s="2" t="n"/>
+      <c r="D153" s="2" t="n">
+        <v>221119000</v>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Farg'ona Qurilish MChJ</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>382544262</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000648973157001</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Плата за SMS-информирование</t>
+          <t>Оплата за продукцию по договору №59/26, НДС 12%</t>
         </is>
       </c>
       <c r="J153" s="2" t="n">
-        <v>428442000</v>
+        <v>534302000</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="3" t="n">
-        <v>46295</v>
+        <v>46289</v>
       </c>
       <c r="B154" t="n">
         <v>246</v>
       </c>
       <c r="C154" s="2" t="n">
-        <v>25042000</v>
+        <v>5441000</v>
       </c>
       <c r="D154" s="2" t="n"/>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Yangi Hayot Yog'och MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>374256960</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>20208000013645912001</t>
+          <t>20208000252939030001</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Оплата за электроэнергию за сентябрь 2026 г.</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="n">
+        <v>528861000</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="3" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B155" t="n">
+        <v>247</v>
+      </c>
+      <c r="C155" s="2" t="n">
+        <v>78358000</v>
+      </c>
+      <c r="D155" s="2" t="n"/>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Farg'ona Avto Savdo XK</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>225696010</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>20208000364591236001</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Предоплата за материалы по договору №217/26</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="n">
+        <v>450503000</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="3" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B156" t="n">
+        <v>248</v>
+      </c>
+      <c r="C156" s="2" t="n">
+        <v>81685000</v>
+      </c>
+      <c r="D156" s="2" t="n"/>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Toshkent Sut Mahsulotlari MChJ</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>304206857</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>20208000071377990001</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
           <t>01153</t>
         </is>
       </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №140/26</t>
-        </is>
-      </c>
-      <c r="J154" s="2" t="n">
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Оплата за сырье по договору №186/26 от 24.09.2026, НДС 12%</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="n">
+        <v>368818000</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="3" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B157" t="n">
+        <v>249</v>
+      </c>
+      <c r="C157" s="2" t="n"/>
+      <c r="D157" s="2" t="n">
+        <v>17970000</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Barakali Qurilish Materiallari MChJ</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>345539163</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>20208000015951773001</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Оплата за продукцию по договору №130/26, НДС 12%</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="n">
+        <v>386788000</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="3" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B158" t="n">
+        <v>250</v>
+      </c>
+      <c r="C158" s="2" t="n"/>
+      <c r="D158" s="2" t="n">
+        <v>10219000</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Farg'ona Qurilish MChJ</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>382544262</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>20208000648973157001</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Оплата по с/ф №3258 за поставленный товар</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="n">
+        <v>397007000</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B159" t="n">
+        <v>251</v>
+      </c>
+      <c r="C159" s="2" t="n"/>
+      <c r="D159" s="2" t="n">
+        <v>33854000</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Farg'ona Qurilish MChJ</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>382544262</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>20208000648973157001</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Предоплата за товар по дог. №59/26 от 28.09.2026</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="n">
+        <v>430861000</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B160" t="n">
+        <v>252</v>
+      </c>
+      <c r="C160" s="2" t="n"/>
+      <c r="D160" s="2" t="n">
+        <v>32876000</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Farg'ona Qurilish MChJ</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>382544262</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>20208000648973157001</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Предоплата за товар по договору №232/26 от 28.09.2026</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="n">
+        <v>463737000</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B161" t="n">
+        <v>253</v>
+      </c>
+      <c r="C161" s="2" t="n"/>
+      <c r="D161" s="2" t="n">
+        <v>7639000</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Farg'ona Qurilish MChJ</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>382544262</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>20208000648973157001</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Предоплата за товар по договору №104/26 от 28.09.2026</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="n">
+        <v>471376000</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B162" t="n">
+        <v>254</v>
+      </c>
+      <c r="C162" s="2" t="n">
+        <v>27027000</v>
+      </c>
+      <c r="D162" s="2" t="n"/>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Saodat Qog'oz AJ</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>330834520</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>20208000955539101001</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Оплата за товары согласно счет-фактуре №4064</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="n">
+        <v>444349000</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B163" t="n">
+        <v>255</v>
+      </c>
+      <c r="C163" s="2" t="n">
+        <v>49322000</v>
+      </c>
+      <c r="D163" s="2" t="n"/>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Toshkent Sut Mahsulotlari MChJ</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>304206857</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>20208000071377990001</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Оплата за товары согласно счет-фактуре №3634</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="n">
+        <v>395027000</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B164" t="n">
+        <v>256</v>
+      </c>
+      <c r="C164" s="2" t="n"/>
+      <c r="D164" s="2" t="n">
+        <v>32574000</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Farg'ona Qurilish MChJ</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>382544262</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>20208000648973157001</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Предоплата за товар по договору №110/26 от 29.09.2026</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="n">
+        <v>427601000</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B165" t="n">
+        <v>257</v>
+      </c>
+      <c r="C165" s="2" t="n">
+        <v>32421000</v>
+      </c>
+      <c r="D165" s="2" t="n"/>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Namangan Non AJ</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>349743926</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>20208000314942583001</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Оплата за товары согласно с/ф №1181</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="n">
+        <v>395180000</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B166" t="n">
+        <v>258</v>
+      </c>
+      <c r="C166" s="2" t="n"/>
+      <c r="D166" s="2" t="n">
+        <v>8520000</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Ishonch Non AJ</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>381564267</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>20208000161840949001</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Оплата по с/ф №2392 за поставленный товар</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="n">
+        <v>403700000</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B167" t="n">
+        <v>259</v>
+      </c>
+      <c r="C167" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D167" s="2" t="n"/>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Navbahor Bank ATB</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>45994000900000001001</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Плата за SMS-информирование</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="n">
         <v>403400000</v>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
+    <row r="168">
+      <c r="A168" t="inlineStr">
         <is>
           <t>Итого обороты:</t>
         </is>
       </c>
-      <c r="C155" s="4" t="n">
-        <v>3429898000</v>
-      </c>
-      <c r="D155" s="4" t="n">
-        <v>3411198000</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
+      <c r="C168" s="4" t="n">
+        <v>3498415000</v>
+      </c>
+      <c r="D168" s="4" t="n">
+        <v>3479715000</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
         <is>
           <t>Исходящий остаток на 30.09.2026:</t>
         </is>
       </c>
-      <c r="C156" s="4" t="n">
+      <c r="C169" s="4" t="n">
         <v>403400000</v>
       </c>
-      <c r="D156" s="4" t="n"/>
+      <c r="D169" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
